--- a/results/CWM vs microclimatic gradients.xlsx
+++ b/results/CWM vs microclimatic gradients.xlsx
@@ -481,19 +481,19 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4">
-        <v>-1.1576269281772899E-5</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.13086526860366E-5</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.00409265612233E-4</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.2967090778461999E-4</v>
       </c>
       <c r="E3" s="3">
-        <v>-1.02366476389064</v>
+        <v>1.5455221918019399</v>
       </c>
       <c r="F3" s="3">
-        <v>0.31134704324235402</v>
+        <v>0.12907269603073701</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -517,19 +517,19 @@
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2.00409265612233E-4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1.2967090778461999E-4</v>
+        <v>7</v>
+      </c>
+      <c r="C5" s="4">
+        <v>-1.1576269281772899E-5</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.13086526860366E-5</v>
       </c>
       <c r="E5" s="3">
-        <v>1.5455221918019399</v>
+        <v>-1.02366476389064</v>
       </c>
       <c r="F5" s="3">
-        <v>0.12907269603073701</v>
+        <v>0.31134704324235402</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -552,22 +552,22 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3">
-        <v>-3.6492416652146597E-4</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.50076199203132E-5</v>
       </c>
       <c r="D7" s="3">
-        <v>5.5138666437433697E-4</v>
+        <v>2.10704057508335E-3</v>
       </c>
       <c r="E7" s="3">
-        <v>-0.66182987384279401</v>
+        <v>7.1226060370097703E-3</v>
       </c>
       <c r="F7" s="3">
-        <v>0.51138224768358498</v>
+        <v>0.99434783120834103</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -576,34 +576,34 @@
         <v>8</v>
       </c>
       <c r="C8" s="3">
-        <v>-4.3666684369097399E-3</v>
+        <v>1.38448828198541E-4</v>
       </c>
       <c r="D8" s="3">
-        <v>6.9999596253341101E-3</v>
+        <v>2.33281602846517E-3</v>
       </c>
       <c r="E8" s="3">
-        <v>-0.62381337473804599</v>
+        <v>5.9348369742482601E-2</v>
       </c>
       <c r="F8" s="3">
-        <v>0.53583154202895</v>
+        <v>0.952931720513711</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3">
-        <v>-1.95187176282332E-2</v>
+        <v>-4.4621567488219898E-4</v>
       </c>
       <c r="D9" s="3">
-        <v>6.3224869747779298E-3</v>
+        <v>1.8375586680230299E-4</v>
       </c>
       <c r="E9" s="3">
-        <v>-3.0871898520469099</v>
+        <v>-2.4283070937934501</v>
       </c>
       <c r="F9" s="5">
-        <v>3.4185369221382601E-3</v>
+        <v>1.91381957284548E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -612,36 +612,36 @@
         <v>10</v>
       </c>
       <c r="C10" s="3">
-        <v>4.0774293337238303E-3</v>
+        <v>2.1003765049539898E-3</v>
       </c>
       <c r="D10" s="3">
-        <v>4.0231036039030301E-3</v>
+        <v>1.34074495764152E-3</v>
       </c>
       <c r="E10" s="3">
-        <v>1.01350343793486</v>
+        <v>1.56657423396074</v>
       </c>
       <c r="F10" s="3">
-        <v>0.31612120521048998</v>
+        <v>0.124068422976049</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C11" s="3">
-        <v>-4.4621567488219898E-4</v>
+        <v>-2.14738597658976E-2</v>
       </c>
       <c r="D11" s="3">
-        <v>1.8375586680230299E-4</v>
+        <v>2.23372095653224E-2</v>
       </c>
       <c r="E11" s="3">
-        <v>-2.4283070937934501</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1.91381957284548E-2</v>
+        <v>-0.96134925461929199</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.34140295332117698</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,72 +650,72 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>1.38448828198541E-4</v>
+        <v>-6.6913175492191298E-3</v>
       </c>
       <c r="D12" s="3">
-        <v>2.33281602846517E-3</v>
+        <v>2.47307057687336E-2</v>
       </c>
       <c r="E12" s="3">
-        <v>5.9348369742482601E-2</v>
+        <v>-0.270567189298689</v>
       </c>
       <c r="F12" s="3">
-        <v>0.952931720513711</v>
+        <v>0.78793426738465899</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1.50076199203132E-5</v>
+      <c r="B13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4.0707710031235803E-3</v>
       </c>
       <c r="D13" s="3">
-        <v>2.10704057508335E-3</v>
+        <v>1.9480371446848701E-3</v>
       </c>
       <c r="E13" s="3">
-        <v>7.1226060370097703E-3</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.99434783120834103</v>
+        <v>2.0896783278647901</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4.2204498343863903E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="3">
-        <v>2.1003765049539898E-3</v>
+        <v>-2.9375316893655301E-2</v>
       </c>
       <c r="D14" s="3">
-        <v>1.34074495764152E-3</v>
+        <v>1.42135379103003E-2</v>
       </c>
       <c r="E14" s="3">
-        <v>1.56657423396074</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.124068422976049</v>
+        <v>-2.06671393702532</v>
+      </c>
+      <c r="F14" s="5">
+        <v>4.4416527822291399E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3">
-        <v>4.0707710031235803E-3</v>
+        <v>0.113412982742257</v>
       </c>
       <c r="D15" s="3">
-        <v>1.9480371446848701E-3</v>
+        <v>3.5238189953985498E-2</v>
       </c>
       <c r="E15" s="3">
-        <v>2.0896783278647901</v>
+        <v>3.21846788641396</v>
       </c>
       <c r="F15" s="5">
-        <v>4.2204498343863903E-2</v>
+        <v>2.3640058146197599E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -724,34 +724,34 @@
         <v>8</v>
       </c>
       <c r="C16" s="3">
-        <v>-6.6913175492191298E-3</v>
+        <v>-4.6183235668440598E-2</v>
       </c>
       <c r="D16" s="3">
-        <v>2.47307057687336E-2</v>
+        <v>3.9014063284237302E-2</v>
       </c>
       <c r="E16" s="3">
-        <v>-0.270567189298689</v>
+        <v>-1.1837586700973</v>
       </c>
       <c r="F16" s="3">
-        <v>0.78793426738465899</v>
+        <v>0.24258985229608299</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" s="3">
-        <v>-2.14738597658976E-2</v>
+        <v>2.1758464952727099E-3</v>
       </c>
       <c r="D17" s="3">
-        <v>2.23372095653224E-2</v>
+        <v>3.0731368992657801E-3</v>
       </c>
       <c r="E17" s="3">
-        <v>-0.96134925461929199</v>
+        <v>0.70802133669754796</v>
       </c>
       <c r="F17" s="3">
-        <v>0.34140295332117698</v>
+        <v>0.48250433702774997</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -760,36 +760,36 @@
         <v>10</v>
       </c>
       <c r="C18" s="3">
-        <v>-2.9375316893655301E-2</v>
+        <v>-6.3789606756303796E-2</v>
       </c>
       <c r="D18" s="3">
-        <v>1.42135379103003E-2</v>
+        <v>2.2422646272652499E-2</v>
       </c>
       <c r="E18" s="3">
-        <v>-2.06671393702532</v>
+        <v>-2.8448741500285801</v>
       </c>
       <c r="F18" s="5">
-        <v>4.4416527822291399E-2</v>
+        <v>6.6111677548571102E-3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C19" s="3">
-        <v>2.1758464952727099E-3</v>
+        <v>0.13585710362469</v>
       </c>
       <c r="D19" s="3">
-        <v>3.0731368992657801E-3</v>
+        <v>3.85282251480457E-2</v>
       </c>
       <c r="E19" s="3">
-        <v>0.70802133669754796</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.48250433702774997</v>
+        <v>3.5261708293765301</v>
+      </c>
+      <c r="F19" s="5">
+        <v>9.6730855965282902E-4</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -798,34 +798,34 @@
         <v>8</v>
       </c>
       <c r="C20" s="3">
-        <v>-4.6183235668440598E-2</v>
+        <v>-3.6667713774892002E-2</v>
       </c>
       <c r="D20" s="3">
-        <v>3.9014063284237302E-2</v>
+        <v>4.2656635205100601E-2</v>
       </c>
       <c r="E20" s="3">
-        <v>-1.1837586700973</v>
+        <v>-0.85960164458793098</v>
       </c>
       <c r="F20" s="3">
-        <v>0.24258985229608299</v>
+        <v>0.394466463946405</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="5" t="s">
-        <v>9</v>
+      <c r="B21" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C21" s="3">
-        <v>0.113412982742257</v>
+        <v>5.1041075287080202E-3</v>
       </c>
       <c r="D21" s="3">
-        <v>3.5238189953985498E-2</v>
+        <v>3.3600622086517699E-3</v>
       </c>
       <c r="E21" s="3">
-        <v>3.21846788641396</v>
-      </c>
-      <c r="F21" s="5">
-        <v>2.3640058146197599E-3</v>
+        <v>1.5190514971911899</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.13559343406204699</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -834,36 +834,36 @@
         <v>10</v>
       </c>
       <c r="C22" s="3">
-        <v>-6.3789606756303796E-2</v>
+        <v>-8.0093821894962905E-2</v>
       </c>
       <c r="D22" s="3">
-        <v>2.2422646272652499E-2</v>
+        <v>2.4516150379342499E-2</v>
       </c>
       <c r="E22" s="3">
-        <v>-2.8448741500285801</v>
+        <v>-3.2669819957724902</v>
       </c>
       <c r="F22" s="5">
-        <v>6.6111677548571102E-3</v>
+        <v>2.0587605513084899E-3</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C23" s="3">
-        <v>5.1041075287080202E-3</v>
+        <v>-1.44106875199717E-3</v>
       </c>
       <c r="D23" s="3">
-        <v>3.3600622086517699E-3</v>
+        <v>1.2251968955540699E-3</v>
       </c>
       <c r="E23" s="3">
-        <v>1.5190514971911899</v>
+        <v>-1.1761936038415199</v>
       </c>
       <c r="F23" s="3">
-        <v>0.13559343406204699</v>
+        <v>0.24556877891332801</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -872,34 +872,34 @@
         <v>8</v>
       </c>
       <c r="C24" s="3">
-        <v>-3.6667713774892002E-2</v>
+        <v>6.9793626012583398E-4</v>
       </c>
       <c r="D24" s="3">
-        <v>4.2656635205100601E-2</v>
+        <v>1.3564802642024199E-3</v>
       </c>
       <c r="E24" s="3">
-        <v>-0.85960164458793098</v>
+        <v>0.51452002549863995</v>
       </c>
       <c r="F24" s="3">
-        <v>0.394466463946405</v>
+        <v>0.60935182891117501</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3">
-        <v>0.13585710362469</v>
+        <v>-2.7354832316146398E-4</v>
       </c>
       <c r="D25" s="3">
-        <v>3.85282251480457E-2</v>
+        <v>1.0684992031400399E-4</v>
       </c>
       <c r="E25" s="3">
-        <v>3.5261708293765301</v>
+        <v>-2.5601172406827999</v>
       </c>
       <c r="F25" s="5">
-        <v>9.6730855965282902E-4</v>
+        <v>1.3813136031488E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -908,36 +908,36 @@
         <v>10</v>
       </c>
       <c r="C26" s="3">
-        <v>-8.0093821894962905E-2</v>
+        <v>2.6947185623422899E-3</v>
       </c>
       <c r="D26" s="3">
-        <v>2.4516150379342499E-2</v>
+        <v>7.7961315945099198E-4</v>
       </c>
       <c r="E26" s="3">
-        <v>-3.2669819957724902</v>
+        <v>3.4564816276830399</v>
       </c>
       <c r="F26" s="5">
-        <v>2.0587605513084899E-3</v>
+        <v>1.1883063224785099E-3</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C27" s="3">
-        <v>-2.7354832316146398E-4</v>
+        <v>-2.76041623672935E-3</v>
       </c>
       <c r="D27" s="3">
-        <v>1.0684992031400399E-4</v>
+        <v>2.1351915530168999E-3</v>
       </c>
       <c r="E27" s="3">
-        <v>-2.5601172406827999</v>
-      </c>
-      <c r="F27" s="5">
-        <v>1.3813136031488E-2</v>
+        <v>-1.2928190132773101</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0.20252953793685599</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -946,34 +946,34 @@
         <v>8</v>
       </c>
       <c r="C28" s="3">
-        <v>6.9793626012583398E-4</v>
+        <v>-2.9628326525507199E-3</v>
       </c>
       <c r="D28" s="3">
-        <v>1.3564802642024199E-3</v>
+        <v>2.3639834645919101E-3</v>
       </c>
       <c r="E28" s="3">
-        <v>0.51452002549863995</v>
+        <v>-1.2533220713801401</v>
       </c>
       <c r="F28" s="3">
-        <v>0.60935182891117501</v>
+        <v>0.216421657367002</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
-      <c r="B29" s="3" t="s">
-        <v>9</v>
+      <c r="B29" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C29" s="3">
-        <v>-1.44106875199717E-3</v>
+        <v>-6.2371143548780802E-4</v>
       </c>
       <c r="D29" s="3">
-        <v>1.2251968955540699E-3</v>
+        <v>1.8621092505447201E-4</v>
       </c>
       <c r="E29" s="3">
-        <v>-1.1761936038415199</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0.24556877891332801</v>
+        <v>-3.3494889481127701</v>
+      </c>
+      <c r="F29" s="5">
+        <v>1.62361763235016E-3</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -982,36 +982,36 @@
         <v>10</v>
       </c>
       <c r="C30" s="3">
-        <v>2.6947185623422899E-3</v>
+        <v>2.84907324426649E-3</v>
       </c>
       <c r="D30" s="3">
-        <v>7.7961315945099198E-4</v>
+        <v>1.35865789304648E-3</v>
       </c>
       <c r="E30" s="3">
-        <v>3.4564816276830399</v>
+        <v>2.09697618425349</v>
       </c>
       <c r="F30" s="5">
-        <v>1.1883063224785099E-3</v>
+        <v>4.1521984589146299E-2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C31" s="3">
-        <v>-6.2371143548780802E-4</v>
+        <v>-1.95187176282332E-2</v>
       </c>
       <c r="D31" s="3">
-        <v>1.8621092505447201E-4</v>
+        <v>6.3224869747779298E-3</v>
       </c>
       <c r="E31" s="3">
-        <v>-3.3494889481127701</v>
+        <v>-3.0871898520469099</v>
       </c>
       <c r="F31" s="5">
-        <v>1.62361763235016E-3</v>
+        <v>3.4185369221382601E-3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1020,65 +1020,65 @@
         <v>8</v>
       </c>
       <c r="C32" s="3">
-        <v>-2.9628326525507199E-3</v>
+        <v>-4.3666684369097399E-3</v>
       </c>
       <c r="D32" s="3">
-        <v>2.3639834645919101E-3</v>
+        <v>6.9999596253341101E-3</v>
       </c>
       <c r="E32" s="3">
-        <v>-1.2533220713801401</v>
+        <v>-0.62381337473804599</v>
       </c>
       <c r="F32" s="3">
-        <v>0.216421657367002</v>
+        <v>0.53583154202895</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33" s="3">
-        <v>-2.76041623672935E-3</v>
+        <v>-3.6492416652146597E-4</v>
       </c>
       <c r="D33" s="3">
-        <v>2.1351915530168999E-3</v>
+        <v>5.5138666437433697E-4</v>
       </c>
       <c r="E33" s="3">
-        <v>-1.2928190132773101</v>
+        <v>-0.66182987384279401</v>
       </c>
       <c r="F33" s="3">
-        <v>0.20252953793685599</v>
+        <v>0.51138224768358498</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="3">
-        <v>2.84907324426649E-3</v>
+        <v>4.0774293337238303E-3</v>
       </c>
       <c r="D34" s="3">
-        <v>1.35865789304648E-3</v>
+        <v>4.0231036039030301E-3</v>
       </c>
       <c r="E34" s="3">
-        <v>2.09697618425349</v>
-      </c>
-      <c r="F34" s="5">
-        <v>4.1521984589146299E-2</v>
+        <v>1.01350343793486</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.31612120521048998</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A31:A34"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A7:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1127,20 +1127,20 @@
       <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>7</v>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C3" s="4">
-        <v>4.151736024893E-5</v>
+        <v>-9.9823423754213E-6</v>
       </c>
       <c r="D3" s="4">
-        <v>8.3353538301871404E-6</v>
+        <v>2.5671441836011299E-5</v>
       </c>
       <c r="E3" s="3">
-        <v>4.9808755686617197</v>
-      </c>
-      <c r="F3" s="6">
-        <v>1.1327316266350701E-5</v>
+        <v>-0.38885008637957702</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.69935146439586704</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1163,20 +1163,20 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
+      <c r="B5" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C5" s="4">
-        <v>-9.9823423754213E-6</v>
+        <v>4.151736024893E-5</v>
       </c>
       <c r="D5" s="4">
-        <v>2.5671441836011299E-5</v>
+        <v>8.3353538301871404E-6</v>
       </c>
       <c r="E5" s="3">
-        <v>-0.38885008637957702</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.69935146439586704</v>
+        <v>4.9808755686617197</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1.1327316266350701E-5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,22 +1199,22 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C7" s="3">
-        <v>-1.1288668474522599E-3</v>
+        <v>1.0425328089413799E-3</v>
       </c>
       <c r="D7" s="3">
-        <v>4.68365629311213E-4</v>
+        <v>1.36706660628985E-3</v>
       </c>
       <c r="E7" s="3">
-        <v>-2.4102256374200599</v>
-      </c>
-      <c r="F7" s="5">
-        <v>2.0399961413703999E-2</v>
+        <v>0.76260571660861998</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.44996056875048801</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1223,34 +1223,34 @@
         <v>8</v>
       </c>
       <c r="C8" s="3">
-        <v>1.1178445468306101E-3</v>
+        <v>-3.4535408694710899E-3</v>
       </c>
       <c r="D8" s="3">
-        <v>3.0580373008893299E-3</v>
+        <v>2.8981523698053402E-3</v>
       </c>
       <c r="E8" s="3">
-        <v>0.365543136607758</v>
+        <v>-1.1916353692967001</v>
       </c>
       <c r="F8" s="3">
-        <v>0.71654063375666499</v>
+        <v>0.24009451827613601</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3">
-        <v>-8.53340901827048E-4</v>
+        <v>7.0555232433820703E-4</v>
       </c>
       <c r="D9" s="3">
-        <v>1.44248477698753E-3</v>
+        <v>4.4387782913207302E-4</v>
       </c>
       <c r="E9" s="3">
-        <v>-0.59157705886446599</v>
+        <v>1.58951918305492</v>
       </c>
       <c r="F9" s="3">
-        <v>0.557304796747775</v>
+        <v>0.119443518272043</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1259,36 +1259,36 @@
         <v>10</v>
       </c>
       <c r="C10" s="3">
-        <v>9.5307541040054596E-4</v>
+        <v>-1.1715617719109601E-3</v>
       </c>
       <c r="D10" s="3">
-        <v>2.1657987529392401E-3</v>
+        <v>2.0525631870242098E-3</v>
       </c>
       <c r="E10" s="3">
-        <v>0.440057234822539</v>
+        <v>-0.57077988113461098</v>
       </c>
       <c r="F10" s="3">
-        <v>0.66215203254689603</v>
+        <v>0.571190346090381</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3">
-        <v>7.0555232433820703E-4</v>
+        <v>3.2977835831519498E-4</v>
       </c>
       <c r="D11" s="3">
-        <v>4.4387782913207302E-4</v>
+        <v>1.19067100620165E-2</v>
       </c>
       <c r="E11" s="3">
-        <v>1.58951918305492</v>
+        <v>2.7696849641717401E-2</v>
       </c>
       <c r="F11" s="3">
-        <v>0.119443518272043</v>
+        <v>0.97803512438198603</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1297,34 +1297,34 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>-3.4535408694710899E-3</v>
+        <v>2.9821060258390002E-4</v>
       </c>
       <c r="D12" s="3">
-        <v>2.8981523698053402E-3</v>
+        <v>2.52419741832988E-2</v>
       </c>
       <c r="E12" s="3">
-        <v>-1.1916353692967001</v>
+        <v>1.1814076047237601E-2</v>
       </c>
       <c r="F12" s="3">
-        <v>0.24009451827613601</v>
+        <v>0.99062989109748201</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
+      <c r="B13" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C13" s="3">
-        <v>1.0425328089413799E-3</v>
+        <v>-8.8105358824538509E-3</v>
       </c>
       <c r="D13" s="3">
-        <v>1.36706660628985E-3</v>
+        <v>3.8660330009643701E-3</v>
       </c>
       <c r="E13" s="3">
-        <v>0.76260571660861998</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.44996056875048801</v>
+        <v>-2.2789603400323002</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2.78165717946358E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1333,36 +1333,36 @@
         <v>10</v>
       </c>
       <c r="C14" s="3">
-        <v>-1.1715617719109601E-3</v>
+        <v>-1.31260776033839E-2</v>
       </c>
       <c r="D14" s="3">
-        <v>2.0525631870242098E-3</v>
+        <v>1.7877164608821002E-2</v>
       </c>
       <c r="E14" s="3">
-        <v>-0.57077988113461098</v>
+        <v>-0.73423710586113899</v>
       </c>
       <c r="F14" s="3">
-        <v>0.571190346090381</v>
+        <v>0.46688377646130103</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="C15" s="3">
-        <v>-8.8105358824538509E-3</v>
+        <v>1.30522817443202E-2</v>
       </c>
       <c r="D15" s="3">
-        <v>3.8660330009643701E-3</v>
+        <v>9.6586805591130694E-3</v>
       </c>
       <c r="E15" s="3">
-        <v>-2.2789603400323002</v>
-      </c>
-      <c r="F15" s="5">
-        <v>2.78165717946358E-2</v>
+        <v>1.35135246107764</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.183816992896734</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1371,34 +1371,34 @@
         <v>8</v>
       </c>
       <c r="C16" s="3">
-        <v>2.9821060258390002E-4</v>
+        <v>1.32007737896713E-3</v>
       </c>
       <c r="D16" s="3">
-        <v>2.52419741832988E-2</v>
+        <v>2.0476199054818699E-2</v>
       </c>
       <c r="E16" s="3">
-        <v>1.1814076047237601E-2</v>
+        <v>6.4468868242246999E-2</v>
       </c>
       <c r="F16" s="3">
-        <v>0.99062989109748201</v>
+        <v>0.94890276959876396</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" s="3">
-        <v>3.2977835831519498E-4</v>
+        <v>2.01496459569483E-3</v>
       </c>
       <c r="D17" s="3">
-        <v>1.19067100620165E-2</v>
+        <v>3.13611212440828E-3</v>
       </c>
       <c r="E17" s="3">
-        <v>2.7696849641717401E-2</v>
+        <v>0.64250400360765603</v>
       </c>
       <c r="F17" s="3">
-        <v>0.97803512438198603</v>
+        <v>0.52403800494076502</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1407,36 +1407,36 @@
         <v>10</v>
       </c>
       <c r="C18" s="3">
-        <v>-1.31260776033839E-2</v>
+        <v>-1.19338009536042E-2</v>
       </c>
       <c r="D18" s="3">
-        <v>1.7877164608821002E-2</v>
+        <v>1.45018919046426E-2</v>
       </c>
       <c r="E18" s="3">
-        <v>-0.73423710586113899</v>
+        <v>-0.82291338482420595</v>
       </c>
       <c r="F18" s="3">
-        <v>0.46688377646130103</v>
+        <v>0.41520526177733902</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="3">
-        <v>2.01496459569483E-3</v>
+        <v>3.3798528562291102E-3</v>
       </c>
       <c r="D19" s="3">
-        <v>3.13611212440828E-3</v>
+        <v>2.3397486385939299E-3</v>
       </c>
       <c r="E19" s="3">
-        <v>0.64250400360765603</v>
+        <v>1.44453673376651</v>
       </c>
       <c r="F19" s="3">
-        <v>0.52403800494076502</v>
+        <v>0.156007523416408</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1445,16 +1445,16 @@
         <v>8</v>
       </c>
       <c r="C20" s="3">
-        <v>1.32007737896713E-3</v>
+        <v>2.46876759400535E-2</v>
       </c>
       <c r="D20" s="3">
-        <v>2.0476199054818699E-2</v>
+        <v>1.52766090501722E-2</v>
       </c>
       <c r="E20" s="3">
-        <v>6.4468868242246999E-2</v>
+        <v>1.6160442320002399</v>
       </c>
       <c r="F20" s="3">
-        <v>0.94890276959876396</v>
+        <v>0.113572646122654</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1463,16 +1463,16 @@
         <v>9</v>
       </c>
       <c r="C21" s="3">
-        <v>1.30522817443202E-2</v>
+        <v>-5.2946600839080804E-4</v>
       </c>
       <c r="D21" s="3">
-        <v>9.6586805591130694E-3</v>
+        <v>7.20601936165225E-3</v>
       </c>
       <c r="E21" s="3">
-        <v>1.35135246107764</v>
+        <v>-7.3475518426779296E-2</v>
       </c>
       <c r="F21" s="3">
-        <v>0.183816992896734</v>
+        <v>0.94177654544017697</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1481,36 +1481,36 @@
         <v>10</v>
       </c>
       <c r="C22" s="3">
-        <v>-1.19338009536042E-2</v>
+        <v>8.8495164216695202E-4</v>
       </c>
       <c r="D22" s="3">
-        <v>1.45018919046426E-2</v>
+        <v>1.0819377782076501E-2</v>
       </c>
       <c r="E22" s="3">
-        <v>-0.82291338482420595</v>
+        <v>8.1793210292829502E-2</v>
       </c>
       <c r="F22" s="3">
-        <v>0.41520526177733902</v>
+        <v>0.93519971051004402</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C23" s="3">
-        <v>3.3798528562291102E-3</v>
+        <v>-4.3837809897109701E-4</v>
       </c>
       <c r="D23" s="3">
-        <v>2.3397486385939299E-3</v>
+        <v>7.2521663648976897E-4</v>
       </c>
       <c r="E23" s="3">
-        <v>1.44453673376651</v>
+        <v>-0.60447882317338697</v>
       </c>
       <c r="F23" s="3">
-        <v>0.156007523416408</v>
+        <v>0.54877713415350704</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1519,34 +1519,34 @@
         <v>8</v>
       </c>
       <c r="C24" s="3">
-        <v>2.46876759400535E-2</v>
+        <v>-1.03664259989497E-3</v>
       </c>
       <c r="D24" s="3">
-        <v>1.52766090501722E-2</v>
+        <v>1.5374439723674E-3</v>
       </c>
       <c r="E24" s="3">
-        <v>1.6160442320002399</v>
+        <v>-0.67426366002704996</v>
       </c>
       <c r="F24" s="3">
-        <v>0.113572646122654</v>
+        <v>0.50383820118974998</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
-      <c r="B25" s="3" t="s">
-        <v>9</v>
+      <c r="B25" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C25" s="3">
-        <v>-5.2946600839080804E-4</v>
+        <v>9.3636653834823502E-4</v>
       </c>
       <c r="D25" s="3">
-        <v>7.20601936165225E-3</v>
+        <v>2.35473227693846E-4</v>
       </c>
       <c r="E25" s="3">
-        <v>-7.3475518426779296E-2</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0.94177654544017697</v>
+        <v>3.9765307823684601</v>
+      </c>
+      <c r="F25" s="5">
+        <v>2.7024275186012903E-4</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1555,36 +1555,36 @@
         <v>10</v>
       </c>
       <c r="C26" s="3">
-        <v>8.8495164216695202E-4</v>
+        <v>2.5846040055292602E-4</v>
       </c>
       <c r="D26" s="3">
-        <v>1.0819377782076501E-2</v>
+        <v>1.0888664559778E-3</v>
       </c>
       <c r="E26" s="3">
-        <v>8.1793210292829502E-2</v>
+        <v>0.23736648248643999</v>
       </c>
       <c r="F26" s="3">
-        <v>0.93519971051004402</v>
+        <v>0.81352656558763603</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C27" s="3">
-        <v>9.3636653834823502E-4</v>
+        <v>2.1084621115094E-3</v>
       </c>
       <c r="D27" s="3">
-        <v>2.35473227693846E-4</v>
+        <v>1.0188594795548999E-3</v>
       </c>
       <c r="E27" s="3">
-        <v>3.9765307823684601</v>
+        <v>2.0694336695287001</v>
       </c>
       <c r="F27" s="5">
-        <v>2.7024275186012903E-4</v>
+        <v>4.46940076626553E-2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1593,34 +1593,34 @@
         <v>8</v>
       </c>
       <c r="C28" s="3">
-        <v>-1.03664259989497E-3</v>
+        <v>-3.6132280813082301E-3</v>
       </c>
       <c r="D28" s="3">
-        <v>1.5374439723674E-3</v>
+        <v>2.15996060585845E-3</v>
       </c>
       <c r="E28" s="3">
-        <v>-0.67426366002704996</v>
+        <v>-1.67282128734575</v>
       </c>
       <c r="F28" s="3">
-        <v>0.50383820118974998</v>
+        <v>0.101796479778928</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29" s="3">
-        <v>-4.3837809897109701E-4</v>
+        <v>-4.0836435255435602E-4</v>
       </c>
       <c r="D29" s="3">
-        <v>7.2521663648976897E-4</v>
+        <v>3.3081719054117302E-4</v>
       </c>
       <c r="E29" s="3">
-        <v>-0.60447882317338697</v>
+        <v>-1.2344109200804401</v>
       </c>
       <c r="F29" s="3">
-        <v>0.54877713415350704</v>
+        <v>0.223912066415312</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1629,36 +1629,36 @@
         <v>10</v>
       </c>
       <c r="C30" s="3">
-        <v>2.5846040055292602E-4</v>
+        <v>-1.33868545038035E-3</v>
       </c>
       <c r="D30" s="3">
-        <v>1.0888664559778E-3</v>
+        <v>1.52975242820147E-3</v>
       </c>
       <c r="E30" s="3">
-        <v>0.23736648248643999</v>
+        <v>-0.87509941197102403</v>
       </c>
       <c r="F30" s="3">
-        <v>0.81352656558763603</v>
+        <v>0.38649692309282502</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C31" s="3">
-        <v>-4.0836435255435602E-4</v>
+        <v>-8.53340901827048E-4</v>
       </c>
       <c r="D31" s="3">
-        <v>3.3081719054117302E-4</v>
+        <v>1.44248477698753E-3</v>
       </c>
       <c r="E31" s="3">
-        <v>-1.2344109200804401</v>
+        <v>-0.59157705886446599</v>
       </c>
       <c r="F31" s="3">
-        <v>0.223912066415312</v>
+        <v>0.557304796747775</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1667,34 +1667,34 @@
         <v>8</v>
       </c>
       <c r="C32" s="3">
-        <v>-3.6132280813082301E-3</v>
+        <v>1.1178445468306101E-3</v>
       </c>
       <c r="D32" s="3">
-        <v>2.15996060585845E-3</v>
+        <v>3.0580373008893299E-3</v>
       </c>
       <c r="E32" s="3">
-        <v>-1.67282128734575</v>
+        <v>0.365543136607758</v>
       </c>
       <c r="F32" s="3">
-        <v>0.101796479778928</v>
+        <v>0.71654063375666499</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33" s="3">
-        <v>2.1084621115094E-3</v>
+        <v>-1.1288668474522599E-3</v>
       </c>
       <c r="D33" s="3">
-        <v>1.0188594795548999E-3</v>
+        <v>4.68365629311213E-4</v>
       </c>
       <c r="E33" s="3">
-        <v>2.0694336695287001</v>
+        <v>-2.4102256374200599</v>
       </c>
       <c r="F33" s="5">
-        <v>4.46940076626553E-2</v>
+        <v>2.0399961413703999E-2</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1703,29 +1703,29 @@
         <v>10</v>
       </c>
       <c r="C34" s="3">
-        <v>-1.33868545038035E-3</v>
+        <v>9.5307541040054596E-4</v>
       </c>
       <c r="D34" s="3">
-        <v>1.52975242820147E-3</v>
+        <v>2.1657987529392401E-3</v>
       </c>
       <c r="E34" s="3">
-        <v>-0.87509941197102403</v>
+        <v>0.440057234822539</v>
       </c>
       <c r="F34" s="3">
-        <v>0.38649692309282502</v>
+        <v>0.66215203254689603</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A31:A34"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A7:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/results/CWM vs microclimatic gradients.xlsx
+++ b/results/CWM vs microclimatic gradients.xlsx
@@ -480,20 +480,20 @@
       <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>2.00409265612233E-4</v>
+        <v>2.9774725631984898E-4</v>
       </c>
       <c r="D3" s="3">
-        <v>1.2967090778461999E-4</v>
+        <v>1.16993495544213E-4</v>
       </c>
       <c r="E3" s="3">
-        <v>1.5455221918019399</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.12907269603073701</v>
+        <v>2.5449898298604801</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1.459847124346E-2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -502,16 +502,16 @@
         <v>8</v>
       </c>
       <c r="C4" s="3">
-        <v>-1.43409388282413E-4</v>
+        <v>-1.00161972804523E-4</v>
       </c>
       <c r="D4" s="3">
-        <v>1.43565518235749E-4</v>
+        <v>1.25332491521214E-4</v>
       </c>
       <c r="E4" s="3">
-        <v>-0.99891248291891899</v>
+        <v>-0.79917004432620797</v>
       </c>
       <c r="F4" s="3">
-        <v>0.32306295846023497</v>
+        <v>0.42858430193186398</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -520,16 +520,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="4">
-        <v>-1.1576269281772899E-5</v>
+        <v>-8.3782146907244201E-6</v>
       </c>
       <c r="D5" s="4">
-        <v>1.13086526860366E-5</v>
+        <v>9.9935671735047501E-6</v>
       </c>
       <c r="E5" s="3">
-        <v>-1.02366476389064</v>
+        <v>-0.83836077201111803</v>
       </c>
       <c r="F5" s="3">
-        <v>0.31134704324235402</v>
+        <v>0.40646437022820397</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -537,17 +537,17 @@
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4">
-        <v>-7.9717715940877298E-5</v>
+      <c r="C6" s="3">
+        <v>-1.03386750160296E-4</v>
       </c>
       <c r="D6" s="4">
-        <v>8.2511755027855297E-5</v>
+        <v>7.3228280855739501E-5</v>
       </c>
       <c r="E6" s="3">
-        <v>-0.96613768443011905</v>
+        <v>-1.41184183149089</v>
       </c>
       <c r="F6" s="3">
-        <v>0.339027454971983</v>
+        <v>0.165192459970259</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -557,17 +557,17 @@
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4">
-        <v>1.50076199203132E-5</v>
+      <c r="C7" s="3">
+        <v>1.55087403884757E-3</v>
       </c>
       <c r="D7" s="3">
-        <v>2.10704057508335E-3</v>
+        <v>2.06829167112347E-3</v>
       </c>
       <c r="E7" s="3">
-        <v>7.1226060370097703E-3</v>
+        <v>0.749833333712143</v>
       </c>
       <c r="F7" s="3">
-        <v>0.99434783120834103</v>
+        <v>0.45743821329579198</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -576,16 +576,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="3">
-        <v>1.38448828198541E-4</v>
+        <v>6.47420690964331E-4</v>
       </c>
       <c r="D8" s="3">
-        <v>2.33281602846517E-3</v>
+        <v>2.21571419102113E-3</v>
       </c>
       <c r="E8" s="3">
-        <v>5.9348369742482601E-2</v>
+        <v>0.29219503742310798</v>
       </c>
       <c r="F8" s="3">
-        <v>0.952931720513711</v>
+        <v>0.77154271780413397</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -594,16 +594,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="3">
-        <v>-4.4621567488219898E-4</v>
+        <v>-4.3337034512231103E-4</v>
       </c>
       <c r="D9" s="3">
-        <v>1.8375586680230299E-4</v>
+        <v>1.76673170193137E-4</v>
       </c>
       <c r="E9" s="3">
-        <v>-2.4283070937934501</v>
+        <v>-2.4529493903831301</v>
       </c>
       <c r="F9" s="5">
-        <v>1.91381957284548E-2</v>
+        <v>1.8300363450988399E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -612,16 +612,16 @@
         <v>10</v>
       </c>
       <c r="C10" s="3">
-        <v>2.1003765049539898E-3</v>
+        <v>2.0331919863242698E-3</v>
       </c>
       <c r="D10" s="3">
-        <v>1.34074495764152E-3</v>
+        <v>1.2945800335316801E-3</v>
       </c>
       <c r="E10" s="3">
-        <v>1.56657423396074</v>
+        <v>1.57054174609631</v>
       </c>
       <c r="F10" s="3">
-        <v>0.124068422976049</v>
+        <v>0.12361936463164901</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -632,16 +632,16 @@
         <v>9</v>
       </c>
       <c r="C11" s="3">
-        <v>-2.14738597658976E-2</v>
+        <v>-3.1534802392588199E-2</v>
       </c>
       <c r="D11" s="3">
-        <v>2.23372095653224E-2</v>
+        <v>2.04545257771463E-2</v>
       </c>
       <c r="E11" s="3">
-        <v>-0.96134925461929199</v>
+        <v>-1.54170293343206</v>
       </c>
       <c r="F11" s="3">
-        <v>0.34140295332117698</v>
+        <v>0.130473678404323</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,16 +650,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>-6.6913175492191298E-3</v>
+        <v>-4.7365595215942699E-3</v>
       </c>
       <c r="D12" s="3">
-        <v>2.47307057687336E-2</v>
+        <v>2.19124718567438E-2</v>
       </c>
       <c r="E12" s="3">
-        <v>-0.270567189298689</v>
+        <v>-0.21615815653114201</v>
       </c>
       <c r="F12" s="3">
-        <v>0.78793426738465899</v>
+        <v>0.82988664605638496</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -668,34 +668,34 @@
         <v>7</v>
       </c>
       <c r="C13" s="3">
-        <v>4.0707710031235803E-3</v>
+        <v>3.67057197340822E-3</v>
       </c>
       <c r="D13" s="3">
-        <v>1.9480371446848701E-3</v>
+        <v>1.74722258194983E-3</v>
       </c>
       <c r="E13" s="3">
-        <v>2.0896783278647901</v>
+        <v>2.1008038765799402</v>
       </c>
       <c r="F13" s="5">
-        <v>4.2204498343863903E-2</v>
+        <v>4.1557955801709602E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="3">
-        <v>-2.9375316893655301E-2</v>
+        <v>-1.8729058261312E-2</v>
       </c>
       <c r="D14" s="3">
-        <v>1.42135379103003E-2</v>
+        <v>1.28028464438331E-2</v>
       </c>
       <c r="E14" s="3">
-        <v>-2.06671393702532</v>
-      </c>
-      <c r="F14" s="5">
-        <v>4.4416527822291399E-2</v>
+        <v>-1.4628823631898999</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.15077106708398699</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -706,16 +706,16 @@
         <v>9</v>
       </c>
       <c r="C15" s="3">
-        <v>0.113412982742257</v>
+        <v>0.11406769778478899</v>
       </c>
       <c r="D15" s="3">
-        <v>3.5238189953985498E-2</v>
+        <v>3.7880674635975102E-2</v>
       </c>
       <c r="E15" s="3">
-        <v>3.21846788641396</v>
+        <v>3.0112372306183501</v>
       </c>
       <c r="F15" s="5">
-        <v>2.3640058146197599E-3</v>
+        <v>4.3440093078692997E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -724,16 +724,16 @@
         <v>8</v>
       </c>
       <c r="C16" s="3">
-        <v>-4.6183235668440598E-2</v>
+        <v>-3.7863528594066602E-2</v>
       </c>
       <c r="D16" s="3">
-        <v>3.9014063284237302E-2</v>
+        <v>4.0580711863908998E-2</v>
       </c>
       <c r="E16" s="3">
-        <v>-1.1837586700973</v>
+        <v>-0.93304249371093595</v>
       </c>
       <c r="F16" s="3">
-        <v>0.24258985229608299</v>
+        <v>0.35600785718410199</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -742,16 +742,16 @@
         <v>7</v>
       </c>
       <c r="C17" s="3">
-        <v>2.1758464952727099E-3</v>
+        <v>2.3443174051112699E-3</v>
       </c>
       <c r="D17" s="3">
-        <v>3.0731368992657801E-3</v>
+        <v>3.2357616531701302E-3</v>
       </c>
       <c r="E17" s="3">
-        <v>0.70802133669754796</v>
+        <v>0.72450249937738798</v>
       </c>
       <c r="F17" s="3">
-        <v>0.48250433702774997</v>
+        <v>0.47268122549541502</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -760,16 +760,16 @@
         <v>10</v>
       </c>
       <c r="C18" s="3">
-        <v>-6.3789606756303796E-2</v>
+        <v>-6.8504383384380196E-2</v>
       </c>
       <c r="D18" s="3">
-        <v>2.2422646272652499E-2</v>
+        <v>2.37101786586057E-2</v>
       </c>
       <c r="E18" s="3">
-        <v>-2.8448741500285801</v>
+        <v>-2.8892394431417099</v>
       </c>
       <c r="F18" s="5">
-        <v>6.6111677548571102E-3</v>
+        <v>6.0270833196018597E-3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -780,16 +780,16 @@
         <v>9</v>
       </c>
       <c r="C19" s="3">
-        <v>0.13585710362469</v>
+        <v>0.12796700793250601</v>
       </c>
       <c r="D19" s="3">
-        <v>3.85282251480457E-2</v>
+        <v>4.2039009362291498E-2</v>
       </c>
       <c r="E19" s="3">
-        <v>3.5261708293765301</v>
+        <v>3.0440062664105301</v>
       </c>
       <c r="F19" s="5">
-        <v>9.6730855965282902E-4</v>
+        <v>3.97359744409058E-3</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -798,16 +798,16 @@
         <v>8</v>
       </c>
       <c r="C20" s="3">
-        <v>-3.6667713774892002E-2</v>
+        <v>-3.3845248217247603E-2</v>
       </c>
       <c r="D20" s="3">
-        <v>4.2656635205100601E-2</v>
+        <v>4.5035442012829698E-2</v>
       </c>
       <c r="E20" s="3">
-        <v>-0.85960164458793098</v>
+        <v>-0.75152472596151598</v>
       </c>
       <c r="F20" s="3">
-        <v>0.394466463946405</v>
+        <v>0.45643067708164098</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -816,16 +816,16 @@
         <v>7</v>
       </c>
       <c r="C21" s="3">
-        <v>5.1041075287080202E-3</v>
+        <v>4.8604570375137598E-3</v>
       </c>
       <c r="D21" s="3">
-        <v>3.3600622086517699E-3</v>
+        <v>3.5909659935828499E-3</v>
       </c>
       <c r="E21" s="3">
-        <v>1.5190514971911899</v>
+        <v>1.35352354942918</v>
       </c>
       <c r="F21" s="3">
-        <v>0.13559343406204699</v>
+        <v>0.18296097934302599</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -834,16 +834,16 @@
         <v>10</v>
       </c>
       <c r="C22" s="3">
-        <v>-8.0093821894962905E-2</v>
+        <v>-8.6173337516371698E-2</v>
       </c>
       <c r="D22" s="3">
-        <v>2.4516150379342499E-2</v>
+        <v>2.6312953298464101E-2</v>
       </c>
       <c r="E22" s="3">
-        <v>-3.2669819957724902</v>
+        <v>-3.2749397811382002</v>
       </c>
       <c r="F22" s="5">
-        <v>2.0587605513084899E-3</v>
+        <v>2.09231991736174E-3</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -854,16 +854,16 @@
         <v>9</v>
       </c>
       <c r="C23" s="3">
-        <v>-1.44106875199717E-3</v>
+        <v>-1.4772131280003601E-3</v>
       </c>
       <c r="D23" s="3">
-        <v>1.2251968955540699E-3</v>
+        <v>1.3561906344612101E-3</v>
       </c>
       <c r="E23" s="3">
-        <v>-1.1761936038415199</v>
+        <v>-1.0892370810297001</v>
       </c>
       <c r="F23" s="3">
-        <v>0.24556877891332801</v>
+        <v>0.282116337490117</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -872,16 +872,16 @@
         <v>8</v>
       </c>
       <c r="C24" s="3">
-        <v>6.9793626012583398E-4</v>
+        <v>3.4071149147597602E-4</v>
       </c>
       <c r="D24" s="3">
-        <v>1.3564802642024199E-3</v>
+        <v>1.45285642081294E-3</v>
       </c>
       <c r="E24" s="3">
-        <v>0.51452002549863995</v>
+        <v>0.23451146761311101</v>
       </c>
       <c r="F24" s="3">
-        <v>0.60935182891117501</v>
+        <v>0.81570102753640605</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -890,16 +890,16 @@
         <v>7</v>
       </c>
       <c r="C25" s="3">
-        <v>-2.7354832316146398E-4</v>
+        <v>-2.90442200904909E-4</v>
       </c>
       <c r="D25" s="3">
-        <v>1.0684992031400399E-4</v>
+        <v>1.15845604428874E-4</v>
       </c>
       <c r="E25" s="3">
-        <v>-2.5601172406827999</v>
+        <v>-2.50714908292642</v>
       </c>
       <c r="F25" s="5">
-        <v>1.3813136031488E-2</v>
+        <v>1.60289209949659E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -908,16 +908,16 @@
         <v>10</v>
       </c>
       <c r="C26" s="3">
-        <v>2.6947185623422899E-3</v>
+        <v>2.4105633771054099E-3</v>
       </c>
       <c r="D26" s="3">
-        <v>7.7961315945099198E-4</v>
+        <v>8.4886350486654695E-4</v>
       </c>
       <c r="E26" s="3">
-        <v>3.4564816276830399</v>
+        <v>2.8397538158792499</v>
       </c>
       <c r="F26" s="5">
-        <v>1.1883063224785099E-3</v>
+        <v>6.8694616916293401E-3</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -928,16 +928,16 @@
         <v>9</v>
       </c>
       <c r="C27" s="3">
-        <v>-2.76041623672935E-3</v>
+        <v>-1.34300593301126E-3</v>
       </c>
       <c r="D27" s="3">
-        <v>2.1351915530168999E-3</v>
+        <v>2.0009059145823E-3</v>
       </c>
       <c r="E27" s="3">
-        <v>-1.2928190132773101</v>
+        <v>-0.67119894205101704</v>
       </c>
       <c r="F27" s="3">
-        <v>0.20252953793685599</v>
+        <v>0.505683616801612</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -946,16 +946,16 @@
         <v>8</v>
       </c>
       <c r="C28" s="3">
-        <v>-2.9628326525507199E-3</v>
+        <v>-1.9955676096857799E-3</v>
       </c>
       <c r="D28" s="3">
-        <v>2.3639834645919101E-3</v>
+        <v>2.1435253507692798E-3</v>
       </c>
       <c r="E28" s="3">
-        <v>-1.2533220713801401</v>
+        <v>-0.93097457838303199</v>
       </c>
       <c r="F28" s="3">
-        <v>0.216421657367002</v>
+        <v>0.35706433979097302</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -964,16 +964,16 @@
         <v>7</v>
       </c>
       <c r="C29" s="3">
-        <v>-6.2371143548780802E-4</v>
+        <v>-5.4434266701940603E-4</v>
       </c>
       <c r="D29" s="3">
-        <v>1.8621092505447201E-4</v>
+        <v>1.7091708878537101E-4</v>
       </c>
       <c r="E29" s="3">
-        <v>-3.3494889481127701</v>
+        <v>-3.1848346522152799</v>
       </c>
       <c r="F29" s="5">
-        <v>1.62361763235016E-3</v>
+        <v>2.6945655171726102E-3</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -982,16 +982,16 @@
         <v>10</v>
       </c>
       <c r="C30" s="3">
-        <v>2.84907324426649E-3</v>
+        <v>2.7234885230941301E-3</v>
       </c>
       <c r="D30" s="3">
-        <v>1.35865789304648E-3</v>
+        <v>1.25240210660746E-3</v>
       </c>
       <c r="E30" s="3">
-        <v>2.09697618425349</v>
+        <v>2.17461189878671</v>
       </c>
       <c r="F30" s="5">
-        <v>4.1521984589146299E-2</v>
+        <v>3.52068642878096E-2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1002,16 +1002,16 @@
         <v>9</v>
       </c>
       <c r="C31" s="3">
-        <v>-1.95187176282332E-2</v>
+        <v>-2.2654158977855301E-2</v>
       </c>
       <c r="D31" s="3">
-        <v>6.3224869747779298E-3</v>
+        <v>6.0799316634404504E-3</v>
       </c>
       <c r="E31" s="3">
-        <v>-3.0871898520469099</v>
+        <v>-3.72605486901739</v>
       </c>
       <c r="F31" s="5">
-        <v>3.4185369221382601E-3</v>
+        <v>5.6260948975973E-4</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1020,16 +1020,16 @@
         <v>8</v>
       </c>
       <c r="C32" s="3">
-        <v>-4.3666684369097399E-3</v>
+        <v>-5.6972391126428002E-3</v>
       </c>
       <c r="D32" s="3">
-        <v>6.9999596253341101E-3</v>
+        <v>6.5132935819473999E-3</v>
       </c>
       <c r="E32" s="3">
-        <v>-0.62381337473804599</v>
+        <v>-0.87470939870322795</v>
       </c>
       <c r="F32" s="3">
-        <v>0.53583154202895</v>
+        <v>0.38659164650328798</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,16 +1038,16 @@
         <v>7</v>
       </c>
       <c r="C33" s="3">
-        <v>-3.6492416652146597E-4</v>
+        <v>-3.9963011233240802E-4</v>
       </c>
       <c r="D33" s="3">
-        <v>5.5138666437433697E-4</v>
+        <v>5.1934686801411801E-4</v>
       </c>
       <c r="E33" s="3">
-        <v>-0.66182987384279401</v>
+        <v>-0.76948593886878702</v>
       </c>
       <c r="F33" s="3">
-        <v>0.51138224768358498</v>
+        <v>0.44581143634832898</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1056,16 +1056,16 @@
         <v>10</v>
       </c>
       <c r="C34" s="3">
-        <v>4.0774293337238303E-3</v>
+        <v>5.0890447137044497E-3</v>
       </c>
       <c r="D34" s="3">
-        <v>4.0231036039030301E-3</v>
+        <v>3.8055358664436799E-3</v>
       </c>
       <c r="E34" s="3">
-        <v>1.01350343793486</v>
+        <v>1.33727414280298</v>
       </c>
       <c r="F34" s="3">
-        <v>0.31612120521048998</v>
+        <v>0.188164451114991</v>
       </c>
     </row>
   </sheetData>
@@ -1131,16 +1131,16 @@
         <v>9</v>
       </c>
       <c r="C3" s="4">
-        <v>-9.9823423754213E-6</v>
+        <v>-1.01430732505203E-5</v>
       </c>
       <c r="D3" s="4">
-        <v>2.5671441836011299E-5</v>
+        <v>2.5717282470552999E-5</v>
       </c>
       <c r="E3" s="3">
-        <v>-0.38885008637957702</v>
+        <v>-0.39440688424736797</v>
       </c>
       <c r="F3" s="3">
-        <v>0.69935146439586704</v>
+        <v>0.69527631074207297</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1149,16 +1149,16 @@
         <v>8</v>
       </c>
       <c r="C4" s="4">
-        <v>-5.4677998653281203E-5</v>
+        <v>-5.4600320055581802E-5</v>
       </c>
       <c r="D4" s="4">
-        <v>5.4422915204749003E-5</v>
+        <v>5.4520096383061098E-5</v>
       </c>
       <c r="E4" s="3">
-        <v>-1.0046870596250199</v>
+        <v>-1.00147145140678</v>
       </c>
       <c r="F4" s="3">
-        <v>0.320801014977454</v>
+        <v>0.32233410282533098</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1167,16 +1167,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="4">
-        <v>4.151736024893E-5</v>
+        <v>4.1533375289601001E-5</v>
       </c>
       <c r="D5" s="4">
-        <v>8.3353538301871404E-6</v>
+        <v>8.3502379925628295E-6</v>
       </c>
       <c r="E5" s="3">
-        <v>4.9808755686617197</v>
+        <v>4.9739151538666198</v>
       </c>
       <c r="F5" s="6">
-        <v>1.1327316266350701E-5</v>
+        <v>1.1585979698418501E-5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1185,16 +1185,16 @@
         <v>10</v>
       </c>
       <c r="C6" s="4">
-        <v>6.1776042219764298E-6</v>
+        <v>6.0816538613657903E-6</v>
       </c>
       <c r="D6" s="4">
-        <v>3.8544030135762303E-5</v>
+        <v>3.8612856920424602E-5</v>
       </c>
       <c r="E6" s="3">
-        <v>0.160273956828522</v>
+        <v>0.157503338173064</v>
       </c>
       <c r="F6" s="3">
-        <v>0.87343365177278098</v>
+        <v>0.87560295860638804</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1205,16 +1205,16 @@
         <v>9</v>
       </c>
       <c r="C7" s="3">
-        <v>1.0425328089413799E-3</v>
+        <v>1.0532194927320899E-3</v>
       </c>
       <c r="D7" s="3">
-        <v>1.36706660628985E-3</v>
+        <v>1.36665481585808E-3</v>
       </c>
       <c r="E7" s="3">
-        <v>0.76260571660861998</v>
+        <v>0.77065509191566095</v>
       </c>
       <c r="F7" s="3">
-        <v>0.44996056875048801</v>
+        <v>0.44522511250969399</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1223,16 +1223,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="3">
-        <v>-3.4535408694710899E-3</v>
+        <v>-3.4641880597359601E-3</v>
       </c>
       <c r="D8" s="3">
-        <v>2.8981523698053402E-3</v>
+        <v>2.89727938277589E-3</v>
       </c>
       <c r="E8" s="3">
-        <v>-1.1916353692967001</v>
+        <v>-1.19566931664592</v>
       </c>
       <c r="F8" s="3">
-        <v>0.24009451827613601</v>
+        <v>0.23853287880740401</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1241,16 +1241,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="3">
-        <v>7.0555232433820703E-4</v>
+        <v>7.0171145085603398E-4</v>
       </c>
       <c r="D9" s="3">
-        <v>4.4387782913207302E-4</v>
+        <v>4.4374412339888501E-4</v>
       </c>
       <c r="E9" s="3">
-        <v>1.58951918305492</v>
+        <v>1.58134252118368</v>
       </c>
       <c r="F9" s="3">
-        <v>0.119443518272043</v>
+        <v>0.121302183768354</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1259,16 +1259,16 @@
         <v>10</v>
       </c>
       <c r="C10" s="3">
-        <v>-1.1715617719109601E-3</v>
+        <v>-1.15370844863724E-3</v>
       </c>
       <c r="D10" s="3">
-        <v>2.0525631870242098E-3</v>
+        <v>2.0519449099943099E-3</v>
       </c>
       <c r="E10" s="3">
-        <v>-0.57077988113461098</v>
+        <v>-0.56225118082748105</v>
       </c>
       <c r="F10" s="3">
-        <v>0.571190346090381</v>
+        <v>0.57693359851514903</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1279,16 +1279,16 @@
         <v>9</v>
       </c>
       <c r="C11" s="3">
-        <v>3.2977835831519498E-4</v>
+        <v>2.29010813288941E-4</v>
       </c>
       <c r="D11" s="3">
-        <v>1.19067100620165E-2</v>
+        <v>1.19154078434042E-2</v>
       </c>
       <c r="E11" s="3">
-        <v>2.7696849641717401E-2</v>
+        <v>1.92197209108299E-2</v>
       </c>
       <c r="F11" s="3">
-        <v>0.97803512438198603</v>
+        <v>0.98475684300518096</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1297,16 +1297,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9821060258390002E-4</v>
+        <v>3.5870195876859599E-4</v>
       </c>
       <c r="D12" s="3">
-        <v>2.52419741832988E-2</v>
+        <v>2.52604132963784E-2</v>
       </c>
       <c r="E12" s="3">
-        <v>1.1814076047237601E-2</v>
+        <v>1.42001619118411E-2</v>
       </c>
       <c r="F12" s="3">
-        <v>0.99062989109748201</v>
+        <v>0.98873753192713298</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1315,16 +1315,16 @@
         <v>7</v>
       </c>
       <c r="C13" s="3">
-        <v>-8.8105358824538509E-3</v>
+        <v>-8.7984432666891894E-3</v>
       </c>
       <c r="D13" s="3">
-        <v>3.8660330009643701E-3</v>
+        <v>3.8688571152414898E-3</v>
       </c>
       <c r="E13" s="3">
-        <v>-2.2789603400323002</v>
+        <v>-2.2741711582026198</v>
       </c>
       <c r="F13" s="5">
-        <v>2.78165717946358E-2</v>
+        <v>2.81278420292508E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1333,16 +1333,16 @@
         <v>10</v>
       </c>
       <c r="C14" s="3">
-        <v>-1.31260776033839E-2</v>
+        <v>-1.32099004887487E-2</v>
       </c>
       <c r="D14" s="3">
-        <v>1.7877164608821002E-2</v>
+        <v>1.7890223771997799E-2</v>
       </c>
       <c r="E14" s="3">
-        <v>-0.73423710586113899</v>
+        <v>-0.73838654323738395</v>
       </c>
       <c r="F14" s="3">
-        <v>0.46688377646130103</v>
+        <v>0.46438581875797202</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1353,16 +1353,16 @@
         <v>9</v>
       </c>
       <c r="C15" s="3">
-        <v>1.30522817443202E-2</v>
+        <v>1.29437848395052E-2</v>
       </c>
       <c r="D15" s="3">
-        <v>9.6586805591130694E-3</v>
+        <v>9.6478836331436307E-3</v>
       </c>
       <c r="E15" s="3">
-        <v>1.35135246107764</v>
+        <v>1.3416190878421399</v>
       </c>
       <c r="F15" s="3">
-        <v>0.183816992896734</v>
+        <v>0.18692878353358899</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1371,16 +1371,16 @@
         <v>8</v>
       </c>
       <c r="C16" s="3">
-        <v>1.32007737896713E-3</v>
+        <v>1.4341842320580501E-3</v>
       </c>
       <c r="D16" s="3">
-        <v>2.0476199054818699E-2</v>
+        <v>2.0453309799503001E-2</v>
       </c>
       <c r="E16" s="3">
-        <v>6.4468868242246999E-2</v>
+        <v>7.0119909497136895E-2</v>
       </c>
       <c r="F16" s="3">
-        <v>0.94890276959876396</v>
+        <v>0.94443103118265703</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,16 +1389,16 @@
         <v>7</v>
       </c>
       <c r="C17" s="3">
-        <v>2.01496459569483E-3</v>
+        <v>2.0546883230515098E-3</v>
       </c>
       <c r="D17" s="3">
-        <v>3.13611212440828E-3</v>
+        <v>3.1326064312411999E-3</v>
       </c>
       <c r="E17" s="3">
-        <v>0.64250400360765603</v>
+        <v>0.65590375559479597</v>
       </c>
       <c r="F17" s="3">
-        <v>0.52403800494076502</v>
+        <v>0.51546332322493904</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1407,16 +1407,16 @@
         <v>10</v>
       </c>
       <c r="C18" s="3">
-        <v>-1.19338009536042E-2</v>
+        <v>-1.2126222470991E-2</v>
       </c>
       <c r="D18" s="3">
-        <v>1.45018919046426E-2</v>
+        <v>1.44856810099605E-2</v>
       </c>
       <c r="E18" s="3">
-        <v>-0.82291338482420595</v>
+        <v>-0.83711787265319504</v>
       </c>
       <c r="F18" s="3">
-        <v>0.41520526177733902</v>
+        <v>0.40726450065396702</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1424,19 +1424,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C19" s="3">
-        <v>3.3798528562291102E-3</v>
+        <v>-5.2956511864252903E-4</v>
       </c>
       <c r="D19" s="3">
-        <v>2.3397486385939299E-3</v>
+        <v>7.2085972023041497E-3</v>
       </c>
       <c r="E19" s="3">
-        <v>1.44453673376651</v>
+        <v>-7.3462992005332003E-2</v>
       </c>
       <c r="F19" s="3">
-        <v>0.156007523416408</v>
+        <v>0.94178645335595201</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1445,34 +1445,34 @@
         <v>8</v>
       </c>
       <c r="C20" s="3">
-        <v>2.46876759400535E-2</v>
+        <v>2.46884840876158E-2</v>
       </c>
       <c r="D20" s="3">
-        <v>1.52766090501722E-2</v>
+        <v>1.52820740179798E-2</v>
       </c>
       <c r="E20" s="3">
-        <v>1.6160442320002399</v>
+        <v>1.61551920626539</v>
       </c>
       <c r="F20" s="3">
-        <v>0.113572646122654</v>
+        <v>0.113686525651881</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C21" s="3">
-        <v>-5.2946600839080804E-4</v>
+        <v>3.3784368262366601E-3</v>
       </c>
       <c r="D21" s="3">
-        <v>7.20601936165225E-3</v>
+        <v>2.3405856470521502E-3</v>
       </c>
       <c r="E21" s="3">
-        <v>-7.3475518426779296E-2</v>
+        <v>1.44341516854623</v>
       </c>
       <c r="F21" s="3">
-        <v>0.94177654544017697</v>
+        <v>0.15632140964080601</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1481,16 +1481,16 @@
         <v>10</v>
       </c>
       <c r="C22" s="3">
-        <v>8.8495164216695202E-4</v>
+        <v>8.8369722574934198E-4</v>
       </c>
       <c r="D22" s="3">
-        <v>1.0819377782076501E-2</v>
+        <v>1.0823248245154E-2</v>
       </c>
       <c r="E22" s="3">
-        <v>8.1793210292829502E-2</v>
+        <v>8.1648060335769101E-2</v>
       </c>
       <c r="F22" s="3">
-        <v>0.93519971051004402</v>
+        <v>0.93531444330006797</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1501,16 +1501,16 @@
         <v>9</v>
       </c>
       <c r="C23" s="3">
-        <v>-4.3837809897109701E-4</v>
+        <v>-4.38594711463649E-4</v>
       </c>
       <c r="D23" s="3">
-        <v>7.2521663648976897E-4</v>
+        <v>7.2528622026980403E-4</v>
       </c>
       <c r="E23" s="3">
-        <v>-0.60447882317338697</v>
+        <v>-0.60471948757070504</v>
       </c>
       <c r="F23" s="3">
-        <v>0.54877713415350704</v>
+        <v>0.54861869856838796</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1519,16 +1519,16 @@
         <v>8</v>
       </c>
       <c r="C24" s="3">
-        <v>-1.03664259989497E-3</v>
+        <v>-1.03704575015299E-3</v>
       </c>
       <c r="D24" s="3">
-        <v>1.5374439723674E-3</v>
+        <v>1.5375914885133401E-3</v>
       </c>
       <c r="E24" s="3">
-        <v>-0.67426366002704996</v>
+        <v>-0.67446116728681904</v>
       </c>
       <c r="F24" s="3">
-        <v>0.50383820118974998</v>
+        <v>0.50371392737994802</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1537,16 +1537,16 @@
         <v>7</v>
       </c>
       <c r="C25" s="3">
-        <v>9.3636653834823502E-4</v>
+        <v>9.3616471199295403E-4</v>
       </c>
       <c r="D25" s="3">
-        <v>2.35473227693846E-4</v>
+        <v>2.3549582110449799E-4</v>
       </c>
       <c r="E25" s="3">
-        <v>3.9765307823684601</v>
+        <v>3.9752922476596502</v>
       </c>
       <c r="F25" s="5">
-        <v>2.7024275186012903E-4</v>
+        <v>2.7126463960704599E-4</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1555,16 +1555,16 @@
         <v>10</v>
       </c>
       <c r="C26" s="3">
-        <v>2.5846040055292602E-4</v>
+        <v>2.59363821817927E-4</v>
       </c>
       <c r="D26" s="3">
-        <v>1.0888664559778E-3</v>
+        <v>1.0889709315788101E-3</v>
       </c>
       <c r="E26" s="3">
-        <v>0.23736648248643999</v>
+        <v>0.23817331968806299</v>
       </c>
       <c r="F26" s="3">
-        <v>0.81352656558763603</v>
+        <v>0.81290486544873597</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1575,16 +1575,16 @@
         <v>9</v>
       </c>
       <c r="C27" s="3">
-        <v>2.1084621115094E-3</v>
+        <v>2.1241888209127002E-3</v>
       </c>
       <c r="D27" s="3">
-        <v>1.0188594795548999E-3</v>
+        <v>1.0194376491173801E-3</v>
       </c>
       <c r="E27" s="3">
-        <v>2.0694336695287001</v>
+        <v>2.0836868471081198</v>
       </c>
       <c r="F27" s="5">
-        <v>4.46940076626553E-2</v>
+        <v>4.3311378083315998E-2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1593,16 +1593,16 @@
         <v>8</v>
       </c>
       <c r="C28" s="3">
-        <v>-3.6132280813082301E-3</v>
+        <v>-3.6283250451208502E-3</v>
       </c>
       <c r="D28" s="3">
-        <v>2.15996060585845E-3</v>
+        <v>2.1611863131355698E-3</v>
       </c>
       <c r="E28" s="3">
-        <v>-1.67282128734575</v>
+        <v>-1.67885805266676</v>
       </c>
       <c r="F28" s="3">
-        <v>0.101796479778928</v>
+        <v>0.10060582878739401</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1611,16 +1611,16 @@
         <v>7</v>
       </c>
       <c r="C29" s="3">
-        <v>-4.0836435255435602E-4</v>
+        <v>-4.1379029139413802E-4</v>
       </c>
       <c r="D29" s="3">
-        <v>3.3081719054117302E-4</v>
+        <v>3.3100491851951802E-4</v>
       </c>
       <c r="E29" s="3">
-        <v>-1.2344109200804401</v>
+        <v>-1.2501031502640301</v>
       </c>
       <c r="F29" s="3">
-        <v>0.223912066415312</v>
+        <v>0.21818259777999299</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1629,16 +1629,16 @@
         <v>10</v>
       </c>
       <c r="C30" s="3">
-        <v>-1.33868545038035E-3</v>
+        <v>-1.31358609321981E-3</v>
       </c>
       <c r="D30" s="3">
-        <v>1.52975242820147E-3</v>
+        <v>1.53062051286855E-3</v>
       </c>
       <c r="E30" s="3">
-        <v>-0.87509941197102403</v>
+        <v>-0.85820494510295198</v>
       </c>
       <c r="F30" s="3">
-        <v>0.38649692309282502</v>
+        <v>0.39565057954891297</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1649,16 +1649,16 @@
         <v>9</v>
       </c>
       <c r="C31" s="3">
-        <v>-8.53340901827048E-4</v>
+        <v>-8.64570891251055E-4</v>
       </c>
       <c r="D31" s="3">
-        <v>1.44248477698753E-3</v>
+        <v>1.4415905777861401E-3</v>
       </c>
       <c r="E31" s="3">
-        <v>-0.59157705886446599</v>
+        <v>-0.59973400532263699</v>
       </c>
       <c r="F31" s="3">
-        <v>0.557304796747775</v>
+        <v>0.55190554052011598</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1667,16 +1667,16 @@
         <v>8</v>
       </c>
       <c r="C32" s="3">
-        <v>1.1178445468306101E-3</v>
+        <v>1.13282013002592E-3</v>
       </c>
       <c r="D32" s="3">
-        <v>3.0580373008893299E-3</v>
+        <v>3.0561416174437199E-3</v>
       </c>
       <c r="E32" s="3">
-        <v>0.365543136607758</v>
+        <v>0.37067003818149702</v>
       </c>
       <c r="F32" s="3">
-        <v>0.71654063375666499</v>
+        <v>0.71274631582570303</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1685,16 +1685,16 @@
         <v>7</v>
       </c>
       <c r="C33" s="3">
-        <v>-1.1288668474522599E-3</v>
+        <v>-1.1230864931580601E-3</v>
       </c>
       <c r="D33" s="3">
-        <v>4.68365629311213E-4</v>
+        <v>4.6807528851984298E-4</v>
       </c>
       <c r="E33" s="3">
-        <v>-2.4102256374200599</v>
+        <v>-2.3993714701528202</v>
       </c>
       <c r="F33" s="5">
-        <v>2.0399961413703999E-2</v>
+        <v>2.09375260180477E-2</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1703,16 +1703,16 @@
         <v>10</v>
       </c>
       <c r="C34" s="3">
-        <v>9.5307541040054596E-4</v>
+        <v>9.2618757253592901E-4</v>
       </c>
       <c r="D34" s="3">
-        <v>2.1657987529392401E-3</v>
+        <v>2.1644561699559399E-3</v>
       </c>
       <c r="E34" s="3">
-        <v>0.440057234822539</v>
+        <v>0.42790775132895398</v>
       </c>
       <c r="F34" s="3">
-        <v>0.66215203254689603</v>
+        <v>0.67090455071906996</v>
       </c>
     </row>
   </sheetData>
